--- a/assessment_forms/007_emotional_and_behavioral_self_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/007_emotional_and_behavioral_self_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>self_assessment_questions</t>
+          <t>self_assessment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions</t>
+          <t>frequency_of_emotions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>how_do_you_feel_most_of_the_time</t>
+          <t>How often do you experience the following emotions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>emotional_intensity</t>
+          <t>emotional_state</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>emotional_intensity</t>
+          <t>What is your current emotional state?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>emotional_patterns</t>
+          <t>emotional_intensity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>emotional_patterns</t>
+          <t>How often do you experience emotional intensity?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,122 +617,122 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>behavioral_patterns</t>
+          <t>Do you engage in the following behavioral patterns?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>emotional_state</t>
+          <t>emotional_state_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>emotional_state</t>
+          <t>What is your emotional state when you experience emotional intensity?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>behavioral_state</t>
+          <t>date_of_last_occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>behavioral_state</t>
+          <t>Date of last occurrence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>emotional_and_behavioral_patterns</t>
+          <t>time_of_last_occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>emotional_and_behavioral_patterns</t>
+          <t>Time of last occurrence</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>emotional_and_behavioral_patterns_2</t>
+          <t>frequency_of_last_occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>emotional_and_behavioral_patterns_2</t>
+          <t>Frequency of last occurrence</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emotional_intensity_2</t>
+          <t>note</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>emotional_intensity_2</t>
+          <t>Additional comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,345 +745,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emotional_state_2</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>emotional_state_2</t>
+          <t>Submitted by</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>behavioral_state_2</t>
+          <t>contact_info</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>behavioral_state_2</t>
+          <t>Contact information</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>date_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>date_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>time_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>time_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>date_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>date_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>time_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>time_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>emotional_state_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>emotional_state_2</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>behavioral_state_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>behavioral_state_2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submitted_by</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1136,14 +837,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sadness</t>
+          <t>sadness</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1153,14 +854,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Anxiety</t>
+          <t>anxiety</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1170,14 +871,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anger</t>
+          <t>anger</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +888,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Frustration</t>
+          <t>frustration</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,14 +905,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Excitement</t>
+          <t>excitement</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1221,14 +922,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Happiness</t>
+          <t>happiness</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1238,194 +939,194 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fear</t>
+          <t>fear</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>guilty</t>
+          <t>guilt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Guilty</t>
+          <t>guilt</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>frequency_of_emotions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>shame</t>
+          <t>disgust</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shame</t>
+          <t>disgust</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>frequency_of_expressed_emotions_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>disgust</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Disgust</t>
+          <t>happy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>emotional_patterns_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>avoiding</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avoiding</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>emotional_patterns_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Emotional</t>
+          <t>anxious</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>emotional_patterns_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>behavioral</t>
+          <t>frustrated</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Behavioral</t>
+          <t>frustrated</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>behavioral_patterns_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>avoiding</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avoiding</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>behavioral_patterns_choices</t>
+          <t>emotional_intensity_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emotional</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emotional</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>behavioral_patterns_choices</t>
+          <t>emotional_intensity_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>behavioral</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Behavioral</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>behavioral_patterns_choices</t>
+          <t>emotional_intensity_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>social</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Social</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>behavioral_patterns_choices</t>
+          <t>emotional_intensity_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>interpersonal</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Interpersonal</t>
+          <t>Almost Daily</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cognitive</t>
+          <t>avoiding</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cognitive</t>
+          <t>avoiding</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>behavioral</t>
+          <t>emotional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Behavioral</t>
+          <t>emotional</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>avoidant</t>
+          <t>behavioral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avoidant</t>
+          <t>behavioral</t>
         </is>
       </c>
     </row>
@@ -1488,656 +1189,197 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aggressive</t>
+          <t>social</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>behavioral_patterns_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>interpersonal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>interpersonal</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>behavioral_patterns_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>cognitive</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>cognitive</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>emotional_state_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>happy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>emotional_state_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>frustrated</t>
+          <t>sad</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frustrated</t>
+          <t>sad</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>emotional_state_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>anxious</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Angry</t>
+          <t>anxious</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>emotional_state_choices</t>
+          <t>emotional_state_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fearful</t>
+          <t>frustrated</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fearful</t>
+          <t>frustrated</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>behavioral_state_choices</t>
+          <t>emotional_state_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>angry</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Happy</t>
+          <t>angry</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>behavioral_state_choices</t>
+          <t>frequency_of_last_occurrence_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sad</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sad</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>behavioral_state_choices</t>
+          <t>frequency_of_last_occurrence_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>anxious</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Anxious</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>behavioral_state_choices</t>
+          <t>frequency_of_last_occurrence_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>frustrated</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Frustrated</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>behavioral_state_choices</t>
+          <t>frequency_of_last_occurrence_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>angry</t>
+          <t>almost_daily</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
-        <is>
-          <t>Angry</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>behavioral_state_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>avoidant</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Avoidant</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>emotional_and_behavioral_patterns_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>emotional_and_behavioral_patterns_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>emotional_and_behavioral_patterns_2_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>emotional_and_behavioral_patterns_2_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>emotional_intensity_2_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>emotional_state_2_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>emotional_state_2_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>behavioral_state_2_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>behavioral_state_2_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>frequently</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Frequently</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>frequency_of_last_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>almost_daily</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Almost Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>frequently</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Frequently</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>frequency_of_first_occurrence_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>almost_daily</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
         <is>
           <t>Almost Daily</t>
         </is>
